--- a/moto/uaefi-moto-pinout.xlsx
+++ b/moto/uaefi-moto-pinout.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Stecker A" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Stecker B" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="EGT" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Teile" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Signale'!$A$1:$M$85</definedName>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +63,10 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -108,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -130,6 +135,7 @@
     <xf numFmtId="2" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -11244,4 +11250,396 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Teil</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Hersteller</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Artikelnummer</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Menge je ECU</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Stecker A (J30)</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Superseal 1.0 Header 34-pol., 90°, Keying 1</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>TE Connectivity</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>6437288-1</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>auf der Platine</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Stecker A Gegenstecker</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Superseal 1.0 Buchsengehäuse 34-pol., Keying 1</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>TE Connectivity</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>4-1437290-0</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Kabelbaum</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Stecker B (J31)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Superseal 1.0 Header 34-pol., 90°, Keying 2</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>TE Connectivity</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>6437288-2</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>auf der Platine</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Stecker B Gegenstecker</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Superseal 1.0 Buchsengehäuse 34-pol., Keying 2</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>TE Connectivity</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>4-1437290-1</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Kabelbaum</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Kontakt 0,5 mm²</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Superseal 1.0 Buchsenkontakt</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>TE Connectivity</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>3-1447221-4</t>
+        </is>
+      </c>
+      <c r="E6" s="5">
+        <f>COUNTIFS(Signale!$G$2:$G$150,"A",Signale!$M$2:$M$150,0.5)+COUNTIFS(Signale!$G$2:$G$150,"B",Signale!$M$2:$M$150,0.5)</f>
+        <v/>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Menge aus Blatt Signale (Querschnitt 0,5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Kontakt 0,75–1,25 mm²</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Superseal 1.0 Buchsenkontakt</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>TE Connectivity</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>3-1447221-3</t>
+        </is>
+      </c>
+      <c r="E7" s="5">
+        <f>COUNTIFS(Signale!$G$2:$G$150,"A",Signale!$M$2:$M$150,"&gt;0.5")+COUNTIFS(Signale!$G$2:$G$150,"B",Signale!$M$2:$M$150,"&gt;0.5")</f>
+        <v/>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Menge aus Blatt Signale (Querschnitt &gt; 0,5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Blindstopfen</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Superseal 1.0 Blindstopfen weiß</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>TE Connectivity</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>4-1437284-3</t>
+        </is>
+      </c>
+      <c r="E8" s="5">
+        <f>'Stecker A'!B38+'Stecker B'!B38</f>
+        <v/>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>für unbelegte Kammern</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Crimpzange</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>CERTI-CRIMP Handzange 1,0 mm Kontakte</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>TE Connectivity</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>1454509-1</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Werkzeug</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>EGT-Buchse (J32–J35)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Mini-Thermoelementbuchse Typ K, Leiterplatte</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Omega</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>PCC-SMP-K</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>auf der Platine</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>EGT-Stecker</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Mini-Thermoelementstecker Typ K</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Omega</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>SMPW-K-M</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>am Fühler, meist schon dran</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Bluetooth (U5)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>JDY-33 Modul</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>HuiCheng</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>LCSC C9900001612</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>bestückt, mit C40/C41 gegen Einschaltproblem</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Quelle Artikelnummern: TE Superseal 1.0 Katalog (1308072-2), Omega Datenblatt PCC-SMP.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>